--- a/research/traditional_assets/database/data/taiwan/taiwan_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0451</v>
+        <v>0.0568</v>
       </c>
       <c r="E2">
-        <v>0.05655</v>
+        <v>0.0784</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>39.31</v>
+        <v>39.62</v>
       </c>
       <c r="L2">
-        <v>0.2348267622461171</v>
+        <v>0.2456292622442653</v>
       </c>
       <c r="M2">
-        <v>11.44</v>
+        <v>50.9396</v>
       </c>
       <c r="N2">
-        <v>0.01778330483444738</v>
+        <v>0.08636758223126483</v>
       </c>
       <c r="O2">
-        <v>0.2910200966675147</v>
+        <v>1.28570418980313</v>
       </c>
       <c r="P2">
-        <v>11.44</v>
+        <v>19.4396</v>
       </c>
       <c r="Q2">
-        <v>0.01778330483444738</v>
+        <v>0.0329596473380807</v>
       </c>
       <c r="R2">
-        <v>0.2910200966675147</v>
+        <v>0.4906511862695608</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.6183794140511507</v>
       </c>
       <c r="U2">
-        <v>393.1</v>
+        <v>327.9</v>
       </c>
       <c r="V2">
-        <v>0.61106793098088</v>
+        <v>0.5559511698880976</v>
       </c>
       <c r="W2">
-        <v>0.04904934847957865</v>
+        <v>0.04565547115462292</v>
       </c>
       <c r="X2">
-        <v>0.1111508126628775</v>
+        <v>0.115398789174397</v>
       </c>
       <c r="Y2">
-        <v>-0.06210146418329884</v>
+        <v>-0.06974331801977413</v>
       </c>
       <c r="Z2">
-        <v>0.08965295629820051</v>
+        <v>0.09987616099071209</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04684293699889257</v>
+        <v>0.06385053785872777</v>
       </c>
       <c r="AC2">
-        <v>-0.04684293699889257</v>
+        <v>-0.06385053785872777</v>
       </c>
       <c r="AD2">
-        <v>1173.8</v>
+        <v>1279.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1173.8</v>
+        <v>1279.5</v>
       </c>
       <c r="AG2">
-        <v>780.6999999999999</v>
+        <v>951.6</v>
       </c>
       <c r="AH2">
-        <v>0.6459743547410709</v>
+        <v>0.6844808216979618</v>
       </c>
       <c r="AI2">
-        <v>0.5845326427966735</v>
+        <v>0.6529726971166114</v>
       </c>
       <c r="AJ2">
-        <v>0.5482443820224718</v>
+        <v>0.6173608407940833</v>
       </c>
       <c r="AK2">
-        <v>0.4834055727554179</v>
+        <v>0.5832311841137534</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of Kaohsiung Co., Ltd. (TWSE:2836)</t>
+          <t>Taipei Star Bank (TPEX:5863)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0341</v>
+        <v>0.068</v>
       </c>
       <c r="E3">
-        <v>0.0755</v>
+        <v>0.079</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>31.7</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L3">
-        <v>0.2523885350318472</v>
+        <v>0.2</v>
       </c>
       <c r="M3">
-        <v>5.82</v>
+        <v>5.06</v>
       </c>
       <c r="N3">
-        <v>0.01108571428571429</v>
+        <v>0.04856046065259117</v>
       </c>
       <c r="O3">
-        <v>0.183596214511041</v>
+        <v>0.6155717761557177</v>
       </c>
       <c r="P3">
-        <v>5.82</v>
+        <v>5.06</v>
       </c>
       <c r="Q3">
-        <v>0.01108571428571429</v>
+        <v>0.04856046065259117</v>
       </c>
       <c r="R3">
-        <v>0.183596214511041</v>
+        <v>0.6155717761557177</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>322.7</v>
+        <v>67.7</v>
       </c>
       <c r="V3">
-        <v>0.6146666666666667</v>
+        <v>0.6497120921305183</v>
       </c>
       <c r="W3">
-        <v>0.05709654178674351</v>
+        <v>0.04035346097201768</v>
       </c>
       <c r="X3">
-        <v>0.07857120120488088</v>
+        <v>0.1275226884860171</v>
       </c>
       <c r="Y3">
-        <v>-0.02147465941813737</v>
+        <v>-0.08716922751399944</v>
       </c>
       <c r="Z3">
-        <v>0.105254336713316</v>
+        <v>0.06787778695293147</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04666578836959836</v>
+        <v>0.0638446679475832</v>
       </c>
       <c r="AC3">
-        <v>-0.04666578836959836</v>
+        <v>-0.0638446679475832</v>
       </c>
       <c r="AD3">
-        <v>701.6</v>
+        <v>329.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>701.6</v>
+        <v>329.5</v>
       </c>
       <c r="AG3">
-        <v>378.9</v>
+        <v>261.8</v>
       </c>
       <c r="AH3">
-        <v>0.5719876080221752</v>
+        <v>0.7597417569748675</v>
       </c>
       <c r="AI3">
-        <v>0.5266476505029275</v>
+        <v>0.635364442730428</v>
       </c>
       <c r="AJ3">
-        <v>0.4191835380019914</v>
+        <v>0.7153005464480875</v>
       </c>
       <c r="AK3">
-        <v>0.3753343239227341</v>
+        <v>0.5806165446884011</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Taipei Star Bank (TPEX:5863)</t>
+          <t>Bank of Kaohsiung Co., Ltd. (TWSE:2836)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0561</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="E4">
-        <v>0.03759999999999999</v>
+        <v>0.07780000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>7.61</v>
+        <v>31.4</v>
       </c>
       <c r="L4">
-        <v>0.1820574162679426</v>
+        <v>0.2612312811980033</v>
       </c>
       <c r="M4">
-        <v>5.62</v>
+        <v>45.8796</v>
       </c>
       <c r="N4">
-        <v>0.04750633981403212</v>
+        <v>0.0944802306425041</v>
       </c>
       <c r="O4">
-        <v>0.7385019710906702</v>
+        <v>1.461133757961783</v>
       </c>
       <c r="P4">
-        <v>5.62</v>
+        <v>14.3796</v>
       </c>
       <c r="Q4">
-        <v>0.04750633981403212</v>
+        <v>0.02961202635914333</v>
       </c>
       <c r="R4">
-        <v>0.7385019710906702</v>
+        <v>0.4579490445859873</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.6865796563178406</v>
       </c>
       <c r="U4">
-        <v>70.40000000000001</v>
+        <v>260.2</v>
       </c>
       <c r="V4">
-        <v>0.595097210481826</v>
+        <v>0.535831960461285</v>
       </c>
       <c r="W4">
-        <v>0.0410021551724138</v>
+        <v>0.05095748133722817</v>
       </c>
       <c r="X4">
-        <v>0.1437304241208741</v>
+        <v>0.103274889862777</v>
       </c>
       <c r="Y4">
-        <v>-0.1027282689484603</v>
+        <v>-0.0523174085255488</v>
       </c>
       <c r="Z4">
-        <v>0.06202700697432853</v>
+        <v>0.1190688459633482</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04702008562818677</v>
+        <v>0.06385640776987232</v>
       </c>
       <c r="AC4">
-        <v>-0.04702008562818677</v>
+        <v>-0.06385640776987232</v>
       </c>
       <c r="AD4">
-        <v>472.2</v>
+        <v>950</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>472.2</v>
+        <v>950</v>
       </c>
       <c r="AG4">
-        <v>401.8</v>
+        <v>689.8</v>
       </c>
       <c r="AH4">
-        <v>0.7996613039796783</v>
+        <v>0.6617442184452494</v>
       </c>
       <c r="AI4">
-        <v>0.698624056813138</v>
+        <v>0.659310153376362</v>
       </c>
       <c r="AJ4">
-        <v>0.7725437415881562</v>
+        <v>0.5868640462821166</v>
       </c>
       <c r="AK4">
-        <v>0.6635838150289016</v>
+        <v>0.5842296942491743</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/taiwan/taiwan_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0568</v>
+        <v>0.06285</v>
       </c>
       <c r="E2">
-        <v>0.0784</v>
+        <v>0.08479999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>39.62</v>
+        <v>31.59</v>
       </c>
       <c r="L2">
-        <v>0.2456292622442653</v>
+        <v>0.2022407170294495</v>
       </c>
       <c r="M2">
-        <v>50.9396</v>
+        <v>5.903</v>
       </c>
       <c r="N2">
-        <v>0.08636758223126483</v>
+        <v>0.008935815924916744</v>
       </c>
       <c r="O2">
-        <v>1.28570418980313</v>
+        <v>0.1868629313073757</v>
       </c>
       <c r="P2">
-        <v>19.4396</v>
+        <v>5.903</v>
       </c>
       <c r="Q2">
-        <v>0.0329596473380807</v>
+        <v>0.008935815924916744</v>
       </c>
       <c r="R2">
-        <v>0.4906511862695608</v>
+        <v>0.1868629313073757</v>
       </c>
       <c r="S2">
-        <v>31.5</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.6183794140511507</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>327.9</v>
+        <v>333.2</v>
       </c>
       <c r="V2">
-        <v>0.5559511698880976</v>
+        <v>0.504389948531638</v>
       </c>
       <c r="W2">
-        <v>0.04565547115462292</v>
+        <v>0.04180026033060638</v>
       </c>
       <c r="X2">
-        <v>0.115398789174397</v>
+        <v>0.07640916259084</v>
       </c>
       <c r="Y2">
-        <v>-0.06974331801977413</v>
+        <v>-0.03460890226023362</v>
       </c>
       <c r="Z2">
-        <v>0.09987616099071209</v>
+        <v>0.0880644979421548</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06385053785872777</v>
+        <v>0.05436048421818149</v>
       </c>
       <c r="AC2">
-        <v>-0.06385053785872777</v>
+        <v>-0.05436048421818149</v>
       </c>
       <c r="AD2">
-        <v>1279.5</v>
+        <v>1124</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1279.5</v>
+        <v>1124</v>
       </c>
       <c r="AG2">
-        <v>951.6</v>
+        <v>790.8</v>
       </c>
       <c r="AH2">
-        <v>0.6844808216979618</v>
+        <v>0.6298330158018604</v>
       </c>
       <c r="AI2">
-        <v>0.6529726971166114</v>
+        <v>0.6097097911581232</v>
       </c>
       <c r="AJ2">
-        <v>0.6173608407940833</v>
+        <v>0.5448532451426209</v>
       </c>
       <c r="AK2">
-        <v>0.5832311841137534</v>
+        <v>0.5236045818711514</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taipei Star Bank (TPEX:5863)</t>
+          <t>Bank of Kaohsiung Co., Ltd. (TWSE:2836)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.068</v>
+        <v>0.0998</v>
       </c>
       <c r="E3">
-        <v>0.079</v>
+        <v>0.24</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>8.220000000000001</v>
+        <v>26.1</v>
       </c>
       <c r="L3">
-        <v>0.2</v>
+        <v>0.2158808933002482</v>
       </c>
       <c r="M3">
-        <v>5.06</v>
+        <v>0.963</v>
       </c>
       <c r="N3">
-        <v>0.04856046065259117</v>
+        <v>0.0018900883218842</v>
       </c>
       <c r="O3">
-        <v>0.6155717761557177</v>
+        <v>0.03689655172413793</v>
       </c>
       <c r="P3">
-        <v>5.06</v>
+        <v>0.963</v>
       </c>
       <c r="Q3">
-        <v>0.04856046065259117</v>
+        <v>0.0018900883218842</v>
       </c>
       <c r="R3">
-        <v>0.6155717761557177</v>
+        <v>0.03689655172413793</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>67.7</v>
+        <v>275.6</v>
       </c>
       <c r="V3">
-        <v>0.6497120921305183</v>
+        <v>0.5409224730127576</v>
       </c>
       <c r="W3">
-        <v>0.04035346097201768</v>
+        <v>0.05456826259669664</v>
       </c>
       <c r="X3">
-        <v>0.1275226884860171</v>
+        <v>0.07684898022233425</v>
       </c>
       <c r="Y3">
-        <v>-0.08716922751399944</v>
+        <v>-0.02228071762563761</v>
       </c>
       <c r="Z3">
-        <v>0.06787778695293147</v>
+        <v>0.1023968832048785</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0638446679475832</v>
+        <v>0.05435692313721775</v>
       </c>
       <c r="AC3">
-        <v>-0.0638446679475832</v>
+        <v>-0.05435692313721775</v>
       </c>
       <c r="AD3">
-        <v>329.5</v>
+        <v>874.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>329.5</v>
+        <v>874.9</v>
       </c>
       <c r="AG3">
-        <v>261.8</v>
+        <v>599.3</v>
       </c>
       <c r="AH3">
-        <v>0.7597417569748675</v>
+        <v>0.6319705287489165</v>
       </c>
       <c r="AI3">
-        <v>0.635364442730428</v>
+        <v>0.6196175637393767</v>
       </c>
       <c r="AJ3">
-        <v>0.7153005464480875</v>
+        <v>0.540494227994228</v>
       </c>
       <c r="AK3">
-        <v>0.5806165446884011</v>
+        <v>0.5273671242520238</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Kaohsiung Co., Ltd. (TWSE:2836)</t>
+          <t>Taipei Star Bank (TPEX:5863)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.04559999999999999</v>
+        <v>0.0259</v>
       </c>
       <c r="E4">
-        <v>0.07780000000000001</v>
+        <v>-0.0704</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>31.4</v>
+        <v>5.49</v>
       </c>
       <c r="L4">
-        <v>0.2612312811980033</v>
+        <v>0.1555240793201133</v>
       </c>
       <c r="M4">
-        <v>45.8796</v>
+        <v>4.94</v>
       </c>
       <c r="N4">
-        <v>0.0944802306425041</v>
+        <v>0.0326935804103243</v>
       </c>
       <c r="O4">
-        <v>1.461133757961783</v>
+        <v>0.8998178506375228</v>
       </c>
       <c r="P4">
-        <v>14.3796</v>
+        <v>4.94</v>
       </c>
       <c r="Q4">
-        <v>0.02961202635914333</v>
+        <v>0.0326935804103243</v>
       </c>
       <c r="R4">
-        <v>0.4579490445859873</v>
+        <v>0.8998178506375228</v>
       </c>
       <c r="S4">
-        <v>31.5</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.6865796563178406</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>260.2</v>
+        <v>57.6</v>
       </c>
       <c r="V4">
-        <v>0.535831960461285</v>
+        <v>0.3812045003309067</v>
       </c>
       <c r="W4">
-        <v>0.05095748133722817</v>
+        <v>0.02903225806451613</v>
       </c>
       <c r="X4">
-        <v>0.103274889862777</v>
+        <v>0.07596934495934576</v>
       </c>
       <c r="Y4">
-        <v>-0.0523174085255488</v>
+        <v>-0.04693708689482963</v>
       </c>
       <c r="Z4">
-        <v>0.1190688459633482</v>
+        <v>0.05952782462057335</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06385640776987232</v>
+        <v>0.05436404529914522</v>
       </c>
       <c r="AC4">
-        <v>-0.06385640776987232</v>
+        <v>-0.05436404529914522</v>
       </c>
       <c r="AD4">
-        <v>950</v>
+        <v>249.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>950</v>
+        <v>249.1</v>
       </c>
       <c r="AG4">
-        <v>689.8</v>
+        <v>191.5</v>
       </c>
       <c r="AH4">
-        <v>0.6617442184452494</v>
+        <v>0.6224387806096952</v>
       </c>
       <c r="AI4">
-        <v>0.659310153376362</v>
+        <v>0.5772885283893395</v>
       </c>
       <c r="AJ4">
-        <v>0.5868640462821166</v>
+        <v>0.5589608873321658</v>
       </c>
       <c r="AK4">
-        <v>0.5842296942491743</v>
+        <v>0.5121690291521798</v>
       </c>
       <c r="AL4">
         <v>0</v>
